--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00946-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00946-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FB12FF7-4B28-4760-B692-07B225015EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01ED53F3-DA1A-4885-B729-920111CD002B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F6AA4F58-74E3-4421-A134-06635D20D0EE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{62097400-5FEE-4790-AEF2-B06A9F552995}"/>
   </bookViews>
   <sheets>
     <sheet name="00946-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1591,24 +1591,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0497B652-4CC3-4B07-83E6-AA187F4B6273}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA341CA7-C1D8-4D9B-92E7-ABF060034D20}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1636,7 +1637,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1666,7 +1667,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1712,7 +1713,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1762,7 +1763,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1816,7 +1817,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1842,7 +1843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1898,7 +1899,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1954,7 +1955,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
@@ -2010,7 +2011,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="49">
         <v>2025</v>
       </c>
@@ -2064,7 +2065,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2120,7 +2121,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2176,7 +2177,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2232,7 +2233,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2288,7 +2289,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2344,7 +2345,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2400,7 +2401,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2456,7 +2457,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2512,7 +2513,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2624,7 +2625,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2680,7 +2681,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>26</v>
       </c>
@@ -2736,7 +2737,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2024</v>
       </c>
@@ -2790,7 +2791,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2846,7 +2847,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2902,7 +2903,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2958,7 +2959,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3014,7 +3015,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3070,7 +3071,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="49" t="s">
         <v>68</v>
       </c>
